--- a/tests/TC-14/results/timetable_all_departments_even.xlsx
+++ b/tests/TC-14/results/timetable_all_departments_even.xlsx
@@ -57,7 +57,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -78,20 +78,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF3BF"/>
+        <bgColor rgb="00FFF3BF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E0E0E0"/>
         <bgColor rgb="00E0E0E0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFDAB3"/>
-        <bgColor rgb="00FFDAB3"/>
+        <fgColor rgb="00C8E6C9"/>
+        <bgColor rgb="00C8E6C9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8E6C9"/>
-        <bgColor rgb="00C8E6C9"/>
+        <fgColor rgb="00FFD0E6"/>
+        <bgColor rgb="00FFD0E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFDAB3"/>
+        <bgColor rgb="00FFDAB3"/>
       </patternFill>
     </fill>
     <fill>
@@ -159,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -167,13 +179,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -183,28 +195,46 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
@@ -663,7 +693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -809,14 +839,21 @@
       </c>
       <c r="C2" s="8" t="inlineStr"/>
       <c r="D2" s="8" t="inlineStr"/>
-      <c r="E2" s="8" t="inlineStr"/>
-      <c r="F2" s="8" t="inlineStr"/>
-      <c r="G2" s="8" t="inlineStr"/>
-      <c r="H2" s="8" t="inlineStr"/>
-      <c r="I2" s="8" t="inlineStr"/>
-      <c r="J2" s="8" t="inlineStr"/>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>CS164
+LAB
+Room: L102
+Dr. Epsilon</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="10" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="11" t="n"/>
       <c r="K2" s="8" t="inlineStr"/>
-      <c r="L2" s="9" t="inlineStr">
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -855,18 +892,25 @@
       <c r="I3" s="8" t="inlineStr"/>
       <c r="J3" s="8" t="inlineStr"/>
       <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="9" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
       <c r="M3" s="8" t="inlineStr"/>
       <c r="N3" s="8" t="inlineStr"/>
-      <c r="O3" s="8" t="inlineStr"/>
-      <c r="P3" s="8" t="inlineStr"/>
-      <c r="Q3" s="8" t="inlineStr"/>
-      <c r="R3" s="8" t="inlineStr"/>
-      <c r="S3" s="8" t="inlineStr"/>
+      <c r="O3" s="13" t="inlineStr">
+        <is>
+          <t>CS161
+LAB
+Room: L102
+Dr. Beta</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="11" t="n"/>
       <c r="T3" s="8" t="inlineStr"/>
       <c r="U3" s="7" t="inlineStr">
         <is>
@@ -885,25 +929,39 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr"/>
-      <c r="D4" s="8" t="inlineStr"/>
-      <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="8" t="inlineStr"/>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>CS163
+LAB
+Room: L101
+Dr. Delta</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="11" t="n"/>
       <c r="G4" s="8" t="inlineStr"/>
       <c r="H4" s="8" t="inlineStr"/>
       <c r="I4" s="8" t="inlineStr"/>
       <c r="J4" s="8" t="inlineStr"/>
       <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="9" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr"/>
-      <c r="O4" s="8" t="inlineStr"/>
-      <c r="P4" s="8" t="inlineStr"/>
-      <c r="Q4" s="8" t="inlineStr"/>
+      <c r="N4" s="15" t="inlineStr">
+        <is>
+          <t>CS160
+LAB
+Room: L102
+Dr. Alpha</t>
+        </is>
+      </c>
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="11" t="n"/>
       <c r="R4" s="8" t="inlineStr"/>
       <c r="S4" s="8" t="inlineStr"/>
       <c r="T4" s="8" t="inlineStr"/>
@@ -924,34 +982,34 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>CS162
+LAB
+Room: L103
+Dr. Gamma</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="11" t="n"/>
       <c r="G5" s="8" t="inlineStr"/>
       <c r="H5" s="8" t="inlineStr"/>
       <c r="I5" s="8" t="inlineStr"/>
       <c r="J5" s="8" t="inlineStr"/>
       <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="9" t="inlineStr">
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
       <c r="M5" s="8" t="inlineStr"/>
       <c r="N5" s="8" t="inlineStr"/>
-      <c r="O5" s="10" t="inlineStr">
-        <is>
-          <t>CS163
-LAB
-Room: L101
-Dr. Vivekraj</t>
-        </is>
-      </c>
-      <c r="P5" s="11" t="n"/>
-      <c r="Q5" s="11" t="n"/>
-      <c r="R5" s="11" t="n"/>
-      <c r="S5" s="12" t="n"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="R5" s="8" t="inlineStr"/>
+      <c r="S5" s="8" t="inlineStr"/>
       <c r="T5" s="8" t="inlineStr"/>
       <c r="U5" s="7" t="inlineStr">
         <is>
@@ -979,7 +1037,7 @@
       <c r="I6" s="8" t="inlineStr"/>
       <c r="J6" s="8" t="inlineStr"/>
       <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="9" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -989,16 +1047,9 @@
       <c r="O6" s="8" t="inlineStr"/>
       <c r="P6" s="8" t="inlineStr"/>
       <c r="Q6" s="8" t="inlineStr"/>
-      <c r="R6" s="13" t="inlineStr">
-        <is>
-          <t>CS208
-LAB
-Room: L102
-Dr. Prabhu</t>
-        </is>
-      </c>
-      <c r="S6" s="11" t="n"/>
-      <c r="T6" s="12" t="n"/>
+      <c r="R6" s="8" t="inlineStr"/>
+      <c r="S6" s="8" t="inlineStr"/>
+      <c r="T6" s="8" t="inlineStr"/>
       <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1006,104 +1057,191 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Course Details</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>Course Code</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>Color</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>Name of the Course</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>Course Co-ordinator</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>LTPSC</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr">
         <is>
           <t>Room Number</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>CS160</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr"/>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>Lab Course 1</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>Dr. Alpha</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>0-0-2-0-2</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr">
+        <is>
+          <t>L102</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>CS161</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr"/>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>Lab Course 2</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>Dr. Beta</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>0-0-2-0-2</t>
+        </is>
+      </c>
+      <c r="F13" s="19" t="inlineStr">
+        <is>
+          <t>L102</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>CS162</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr"/>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>Lab Course 3</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>Dr. Gamma</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>0-0-2-0-2</t>
+        </is>
+      </c>
+      <c r="F14" s="19" t="inlineStr">
+        <is>
+          <t>L103</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>CS163</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr"/>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>DSA</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>Dr. Vivekraj</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr"/>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>Lab Course 4</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>Dr. Delta</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
         <is>
           <t>0-0-2-0-2</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F15" s="19" t="inlineStr">
         <is>
           <t>L101</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>CS208</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr"/>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>Comp Arch</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>Dr. Prabhu</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>CS164</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr"/>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Lab Course 5</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Dr. Epsilon</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>0-0-2-0-2</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>L102</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="O5:S5"/>
-    <mergeCell ref="R6:T6"/>
+  <mergeCells count="5">
+    <mergeCell ref="O3:S3"/>
+    <mergeCell ref="E2:J2"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="N4:Q4"/>
+    <mergeCell ref="C5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1116,7 +1254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1262,14 +1400,21 @@
       </c>
       <c r="C2" s="8" t="inlineStr"/>
       <c r="D2" s="8" t="inlineStr"/>
-      <c r="E2" s="8" t="inlineStr"/>
-      <c r="F2" s="8" t="inlineStr"/>
-      <c r="G2" s="8" t="inlineStr"/>
-      <c r="H2" s="8" t="inlineStr"/>
-      <c r="I2" s="8" t="inlineStr"/>
-      <c r="J2" s="8" t="inlineStr"/>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>CS164
+LAB
+Room: L102
+Dr. Epsilon</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="10" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="11" t="n"/>
       <c r="K2" s="8" t="inlineStr"/>
-      <c r="L2" s="9" t="inlineStr">
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1308,18 +1453,25 @@
       <c r="I3" s="8" t="inlineStr"/>
       <c r="J3" s="8" t="inlineStr"/>
       <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="9" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
       <c r="M3" s="8" t="inlineStr"/>
       <c r="N3" s="8" t="inlineStr"/>
-      <c r="O3" s="8" t="inlineStr"/>
-      <c r="P3" s="8" t="inlineStr"/>
-      <c r="Q3" s="8" t="inlineStr"/>
-      <c r="R3" s="8" t="inlineStr"/>
-      <c r="S3" s="8" t="inlineStr"/>
+      <c r="O3" s="13" t="inlineStr">
+        <is>
+          <t>CS161
+LAB
+Room: L102
+Dr. Beta</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="11" t="n"/>
       <c r="T3" s="8" t="inlineStr"/>
       <c r="U3" s="7" t="inlineStr">
         <is>
@@ -1338,25 +1490,39 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr"/>
-      <c r="D4" s="8" t="inlineStr"/>
-      <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="8" t="inlineStr"/>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>CS163
+LAB
+Room: L101
+Dr. Delta</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="11" t="n"/>
       <c r="G4" s="8" t="inlineStr"/>
       <c r="H4" s="8" t="inlineStr"/>
       <c r="I4" s="8" t="inlineStr"/>
       <c r="J4" s="8" t="inlineStr"/>
       <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="9" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr"/>
-      <c r="O4" s="8" t="inlineStr"/>
-      <c r="P4" s="8" t="inlineStr"/>
-      <c r="Q4" s="8" t="inlineStr"/>
+      <c r="N4" s="15" t="inlineStr">
+        <is>
+          <t>CS160
+LAB
+Room: L102
+Dr. Alpha</t>
+        </is>
+      </c>
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="11" t="n"/>
       <c r="R4" s="8" t="inlineStr"/>
       <c r="S4" s="8" t="inlineStr"/>
       <c r="T4" s="8" t="inlineStr"/>
@@ -1377,34 +1543,34 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>CS162
+LAB
+Room: L103
+Dr. Gamma</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="11" t="n"/>
       <c r="G5" s="8" t="inlineStr"/>
       <c r="H5" s="8" t="inlineStr"/>
       <c r="I5" s="8" t="inlineStr"/>
       <c r="J5" s="8" t="inlineStr"/>
       <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="9" t="inlineStr">
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
       <c r="M5" s="8" t="inlineStr"/>
       <c r="N5" s="8" t="inlineStr"/>
-      <c r="O5" s="10" t="inlineStr">
-        <is>
-          <t>CS163
-LAB
-Room: L101
-Dr. Vivekraj</t>
-        </is>
-      </c>
-      <c r="P5" s="11" t="n"/>
-      <c r="Q5" s="11" t="n"/>
-      <c r="R5" s="11" t="n"/>
-      <c r="S5" s="12" t="n"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="R5" s="8" t="inlineStr"/>
+      <c r="S5" s="8" t="inlineStr"/>
       <c r="T5" s="8" t="inlineStr"/>
       <c r="U5" s="7" t="inlineStr">
         <is>
@@ -1432,7 +1598,7 @@
       <c r="I6" s="8" t="inlineStr"/>
       <c r="J6" s="8" t="inlineStr"/>
       <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="9" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1442,16 +1608,9 @@
       <c r="O6" s="8" t="inlineStr"/>
       <c r="P6" s="8" t="inlineStr"/>
       <c r="Q6" s="8" t="inlineStr"/>
-      <c r="R6" s="13" t="inlineStr">
-        <is>
-          <t>CS208
-LAB
-Room: L102
-Dr. Prabhu</t>
-        </is>
-      </c>
-      <c r="S6" s="11" t="n"/>
-      <c r="T6" s="12" t="n"/>
+      <c r="R6" s="8" t="inlineStr"/>
+      <c r="S6" s="8" t="inlineStr"/>
+      <c r="T6" s="8" t="inlineStr"/>
       <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1459,104 +1618,191 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Course Details</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>Course Code</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>Color</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>Name of the Course</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>Course Co-ordinator</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>LTPSC</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr">
         <is>
           <t>Room Number</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>CS160</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr"/>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>Lab Course 1</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>Dr. Alpha</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>0-0-2-0-2</t>
+        </is>
+      </c>
+      <c r="F12" s="19" t="inlineStr">
+        <is>
+          <t>L102</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>CS161</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr"/>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>Lab Course 2</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>Dr. Beta</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>0-0-2-0-2</t>
+        </is>
+      </c>
+      <c r="F13" s="19" t="inlineStr">
+        <is>
+          <t>L102</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>CS162</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr"/>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>Lab Course 3</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>Dr. Gamma</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>0-0-2-0-2</t>
+        </is>
+      </c>
+      <c r="F14" s="19" t="inlineStr">
+        <is>
+          <t>L103</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>CS163</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr"/>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>DSA</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>Dr. Vivekraj</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr"/>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>Lab Course 4</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>Dr. Delta</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
         <is>
           <t>0-0-2-0-2</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F15" s="19" t="inlineStr">
         <is>
           <t>L101</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>CS208</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr"/>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>Comp Arch</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>Dr. Prabhu</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>CS164</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr"/>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Lab Course 5</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Dr. Epsilon</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>0-0-2-0-2</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>L102</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="O5:S5"/>
-    <mergeCell ref="R6:T6"/>
+  <mergeCells count="5">
+    <mergeCell ref="O3:S3"/>
+    <mergeCell ref="E2:J2"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="N4:Q4"/>
+    <mergeCell ref="C5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1568,7 +1814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1620,22 +1866,22 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
         <v>5</v>
       </c>
-      <c r="C2" t="n">
-        <v>15</v>
-      </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dr. Vivekraj</t>
+          <t>Dr. Epsilon</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>L101</t>
+          <t>L102</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1645,7 +1891,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>CS164</t>
         </is>
       </c>
     </row>
@@ -1656,17 +1902,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dr. Prabhu</t>
+          <t>Dr. Beta</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1681,28 +1927,28 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CS208</t>
+          <t>CS161</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CSE_2_B</t>
+          <t>CSE_2_A</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dr. Vivekraj</t>
+          <t>Dr. Delta</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1724,36 +1970,252 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>CSE_2_A</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>14</v>
+      </c>
+      <c r="D5" t="n">
+        <v>17</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Dr. Alpha</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>L102</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CS160</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CSE_2_A</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Dr. Gamma</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>L103</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>CS162</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>CSE_2_B</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Dr. Epsilon</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>L102</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>CS164</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>15</v>
+      </c>
+      <c r="D8" t="n">
+        <v>19</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Dr. Beta</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>L102</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>CS161</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
         <v>6</v>
       </c>
-      <c r="C5" t="n">
-        <v>18</v>
-      </c>
-      <c r="D5" t="n">
-        <v>20</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Dr. Prabhu</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Dr. Delta</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>L101</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>CS163</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" t="n">
+        <v>14</v>
+      </c>
+      <c r="D10" t="n">
+        <v>17</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Dr. Alpha</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>L102</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>LAB</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>CS208</t>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>CS160</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Dr. Gamma</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>L103</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>CS162</t>
         </is>
       </c>
     </row>

--- a/tests/TC-14/results/timetable_all_departments_even.xlsx
+++ b/tests/TC-14/results/timetable_all_departments_even.xlsx
@@ -78,8 +78,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3BF"/>
-        <bgColor rgb="00FFF3BF"/>
+        <fgColor rgb="00FFD0E6"/>
+        <bgColor rgb="00FFD0E6"/>
       </patternFill>
     </fill>
     <fill>
@@ -96,8 +96,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFD0E6"/>
-        <bgColor rgb="00FFD0E6"/>
+        <fgColor rgb="00FFF3BF"/>
+        <bgColor rgb="00FFF3BF"/>
       </patternFill>
     </fill>
     <fill>
@@ -203,6 +203,9 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -210,9 +213,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -231,10 +231,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
@@ -841,10 +841,10 @@
       <c r="D2" s="8" t="inlineStr"/>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>CS164
+          <t>CS163
 LAB
-Room: L102
-Dr. Epsilon</t>
+Room: L103
+Dr. Delta</t>
         </is>
       </c>
       <c r="F2" s="10" t="n"/>
@@ -863,9 +863,16 @@
       <c r="O2" s="8" t="inlineStr"/>
       <c r="P2" s="8" t="inlineStr"/>
       <c r="Q2" s="8" t="inlineStr"/>
-      <c r="R2" s="8" t="inlineStr"/>
-      <c r="S2" s="8" t="inlineStr"/>
-      <c r="T2" s="8" t="inlineStr"/>
+      <c r="R2" s="13" t="inlineStr">
+        <is>
+          <t>CS162
+LAB
+Room: L103
+Dr. Gamma</t>
+        </is>
+      </c>
+      <c r="S2" s="10" t="n"/>
+      <c r="T2" s="11" t="n"/>
       <c r="U2" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -899,42 +906,35 @@
       </c>
       <c r="M3" s="8" t="inlineStr"/>
       <c r="N3" s="8" t="inlineStr"/>
-      <c r="O3" s="13" t="inlineStr">
+      <c r="O3" s="8" t="inlineStr"/>
+      <c r="P3" s="8" t="inlineStr"/>
+      <c r="Q3" s="8" t="inlineStr"/>
+      <c r="R3" s="8" t="inlineStr"/>
+      <c r="S3" s="8" t="inlineStr"/>
+      <c r="T3" s="8" t="inlineStr"/>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>CS161
 LAB
-Room: L102
+Room: L103
 Dr. Beta</t>
-        </is>
-      </c>
-      <c r="P3" s="10" t="n"/>
-      <c r="Q3" s="10" t="n"/>
-      <c r="R3" s="10" t="n"/>
-      <c r="S3" s="11" t="n"/>
-      <c r="T3" s="8" t="inlineStr"/>
-      <c r="U3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>CS163
-LAB
-Room: L101
-Dr. Delta</t>
         </is>
       </c>
       <c r="D4" s="10" t="n"/>
@@ -953,10 +953,10 @@
       <c r="M4" s="8" t="inlineStr"/>
       <c r="N4" s="15" t="inlineStr">
         <is>
-          <t>CS160
+          <t>CS164
 LAB
-Room: L102
-Dr. Alpha</t>
+Room: L101
+Dr. Epsilon</t>
         </is>
       </c>
       <c r="O4" s="10" t="n"/>
@@ -982,17 +982,10 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>CS162
-LAB
-Room: L103
-Dr. Gamma</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="n"/>
-      <c r="E5" s="10" t="n"/>
-      <c r="F5" s="11" t="n"/>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr"/>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
       <c r="G5" s="8" t="inlineStr"/>
       <c r="H5" s="8" t="inlineStr"/>
       <c r="I5" s="8" t="inlineStr"/>
@@ -1005,11 +998,18 @@
       </c>
       <c r="M5" s="8" t="inlineStr"/>
       <c r="N5" s="8" t="inlineStr"/>
-      <c r="O5" s="8" t="inlineStr"/>
-      <c r="P5" s="8" t="inlineStr"/>
-      <c r="Q5" s="8" t="inlineStr"/>
-      <c r="R5" s="8" t="inlineStr"/>
-      <c r="S5" s="8" t="inlineStr"/>
+      <c r="O5" s="16" t="inlineStr">
+        <is>
+          <t>CS160
+LAB
+Room: L102
+Dr. Alpha</t>
+        </is>
+      </c>
+      <c r="P5" s="10" t="n"/>
+      <c r="Q5" s="10" t="n"/>
+      <c r="R5" s="10" t="n"/>
+      <c r="S5" s="11" t="n"/>
       <c r="T5" s="8" t="inlineStr"/>
       <c r="U5" s="7" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>L102</t>
+          <t>L103</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
-          <t>L101</t>
+          <t>L103</t>
         </is>
       </c>
     </row>
@@ -1231,17 +1231,17 @@
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>L102</t>
+          <t>L101</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="O3:S3"/>
     <mergeCell ref="E2:J2"/>
+    <mergeCell ref="R2:T2"/>
     <mergeCell ref="C4:F4"/>
+    <mergeCell ref="O5:S5"/>
     <mergeCell ref="N4:Q4"/>
-    <mergeCell ref="C5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1402,10 +1402,10 @@
       <c r="D2" s="8" t="inlineStr"/>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>CS164
+          <t>CS163
 LAB
-Room: L102
-Dr. Epsilon</t>
+Room: L103
+Dr. Delta</t>
         </is>
       </c>
       <c r="F2" s="10" t="n"/>
@@ -1424,9 +1424,16 @@
       <c r="O2" s="8" t="inlineStr"/>
       <c r="P2" s="8" t="inlineStr"/>
       <c r="Q2" s="8" t="inlineStr"/>
-      <c r="R2" s="8" t="inlineStr"/>
-      <c r="S2" s="8" t="inlineStr"/>
-      <c r="T2" s="8" t="inlineStr"/>
+      <c r="R2" s="13" t="inlineStr">
+        <is>
+          <t>CS162
+LAB
+Room: L103
+Dr. Gamma</t>
+        </is>
+      </c>
+      <c r="S2" s="10" t="n"/>
+      <c r="T2" s="11" t="n"/>
       <c r="U2" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1460,42 +1467,35 @@
       </c>
       <c r="M3" s="8" t="inlineStr"/>
       <c r="N3" s="8" t="inlineStr"/>
-      <c r="O3" s="13" t="inlineStr">
+      <c r="O3" s="8" t="inlineStr"/>
+      <c r="P3" s="8" t="inlineStr"/>
+      <c r="Q3" s="8" t="inlineStr"/>
+      <c r="R3" s="8" t="inlineStr"/>
+      <c r="S3" s="8" t="inlineStr"/>
+      <c r="T3" s="8" t="inlineStr"/>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>CS161
 LAB
-Room: L102
+Room: L103
 Dr. Beta</t>
-        </is>
-      </c>
-      <c r="P3" s="10" t="n"/>
-      <c r="Q3" s="10" t="n"/>
-      <c r="R3" s="10" t="n"/>
-      <c r="S3" s="11" t="n"/>
-      <c r="T3" s="8" t="inlineStr"/>
-      <c r="U3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>CS163
-LAB
-Room: L101
-Dr. Delta</t>
         </is>
       </c>
       <c r="D4" s="10" t="n"/>
@@ -1514,10 +1514,10 @@
       <c r="M4" s="8" t="inlineStr"/>
       <c r="N4" s="15" t="inlineStr">
         <is>
-          <t>CS160
+          <t>CS164
 LAB
-Room: L102
-Dr. Alpha</t>
+Room: L101
+Dr. Epsilon</t>
         </is>
       </c>
       <c r="O4" s="10" t="n"/>
@@ -1543,17 +1543,10 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>CS162
-LAB
-Room: L103
-Dr. Gamma</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="n"/>
-      <c r="E5" s="10" t="n"/>
-      <c r="F5" s="11" t="n"/>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr"/>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
       <c r="G5" s="8" t="inlineStr"/>
       <c r="H5" s="8" t="inlineStr"/>
       <c r="I5" s="8" t="inlineStr"/>
@@ -1566,11 +1559,18 @@
       </c>
       <c r="M5" s="8" t="inlineStr"/>
       <c r="N5" s="8" t="inlineStr"/>
-      <c r="O5" s="8" t="inlineStr"/>
-      <c r="P5" s="8" t="inlineStr"/>
-      <c r="Q5" s="8" t="inlineStr"/>
-      <c r="R5" s="8" t="inlineStr"/>
-      <c r="S5" s="8" t="inlineStr"/>
+      <c r="O5" s="16" t="inlineStr">
+        <is>
+          <t>CS160
+LAB
+Room: L102
+Dr. Alpha</t>
+        </is>
+      </c>
+      <c r="P5" s="10" t="n"/>
+      <c r="Q5" s="10" t="n"/>
+      <c r="R5" s="10" t="n"/>
+      <c r="S5" s="11" t="n"/>
       <c r="T5" s="8" t="inlineStr"/>
       <c r="U5" s="7" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="F13" s="19" t="inlineStr">
         <is>
-          <t>L102</t>
+          <t>L103</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="F15" s="19" t="inlineStr">
         <is>
-          <t>L101</t>
+          <t>L103</t>
         </is>
       </c>
     </row>
@@ -1792,17 +1792,17 @@
       </c>
       <c r="F16" s="19" t="inlineStr">
         <is>
-          <t>L102</t>
+          <t>L101</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="O3:S3"/>
     <mergeCell ref="E2:J2"/>
+    <mergeCell ref="R2:T2"/>
     <mergeCell ref="C4:F4"/>
+    <mergeCell ref="O5:S5"/>
     <mergeCell ref="N4:Q4"/>
-    <mergeCell ref="C5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1876,12 +1876,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dr. Epsilon</t>
+          <t>Dr. Delta</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>L102</t>
+          <t>L103</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CS164</t>
+          <t>CS163</t>
         </is>
       </c>
     </row>
@@ -1902,22 +1902,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dr. Beta</t>
+          <t>Dr. Gamma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>L102</t>
+          <t>L103</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CS161</t>
+          <t>CS162</t>
         </is>
       </c>
     </row>
@@ -1948,12 +1948,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dr. Delta</t>
+          <t>Dr. Beta</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>L101</t>
+          <t>L103</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>CS161</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dr. Alpha</t>
+          <t>Dr. Epsilon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>L102</t>
+          <t>L101</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CS160</t>
+          <t>CS164</t>
         </is>
       </c>
     </row>
@@ -2013,19 +2013,19 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dr. Gamma</t>
+          <t>Dr. Alpha</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>L103</t>
+          <t>L102</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CS162</t>
+          <t>CS160</t>
         </is>
       </c>
     </row>
@@ -2056,12 +2056,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dr. Epsilon</t>
+          <t>Dr. Delta</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>L102</t>
+          <t>L103</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CS164</t>
+          <t>CS163</t>
         </is>
       </c>
     </row>
@@ -2082,22 +2082,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dr. Beta</t>
+          <t>Dr. Gamma</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>L102</t>
+          <t>L103</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>CS161</t>
+          <t>CS162</t>
         </is>
       </c>
     </row>
@@ -2128,12 +2128,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dr. Delta</t>
+          <t>Dr. Beta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>L101</t>
+          <t>L103</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>CS161</t>
         </is>
       </c>
     </row>
@@ -2164,12 +2164,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dr. Alpha</t>
+          <t>Dr. Epsilon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>L102</t>
+          <t>L101</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CS160</t>
+          <t>CS164</t>
         </is>
       </c>
     </row>
@@ -2193,19 +2193,19 @@
         <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dr. Gamma</t>
+          <t>Dr. Alpha</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>L103</t>
+          <t>L102</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CS162</t>
+          <t>CS160</t>
         </is>
       </c>
     </row>
